--- a/docs/downloads/Brantford.xlsx
+++ b/docs/downloads/Brantford.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -457,17 +457,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Gauvreau</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>richard@pickleplexclub.ca</t>
+          <t>s.gauvreau@treefrog.ca</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,15 +479,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Erica</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Martin</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>Gulliver</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ericasgulliver@gmail.com</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -497,15 +501,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Blake</t>
+          <t>Jenny</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Martin</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>Cho</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>tojencho@gmail.com</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -515,15 +523,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Samantha</t>
+          <t>Aitor</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Martin</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>Mendez</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>aitorvmendez@gmail.com</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -533,17 +545,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bernard</t>
+          <t>Tricia</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>French</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bernard@pickleplexclub.ca</t>
+          <t>tricia.french1974@gmail.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -555,15 +567,19 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fineas</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Haw</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>Blakney</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>lindablakney@gmail.com</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -573,15 +589,19 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Anna Laine</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Williams</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>Spector</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>davidspector1961@gmail.com</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -591,15 +611,19 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Yeshe</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Williams</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>Richard</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mik_r87@hotmail.com</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -609,15 +633,19 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>ANDREA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lewis</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>Galvez</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>astmanahan@gmail.com</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -627,15 +655,19 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jadea</t>
+          <t>Martha</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Collin</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>Daikos</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>mdaikos@hotmail.com</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -645,15 +677,19 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tyrese</t>
+          <t>FRANCES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Collin</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>Galvez</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>flmgalvez@gmail.com</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -663,17 +699,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sunny</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mattu</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>matsunny@gmail.com</t>
+          <t>richard@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -685,15 +721,19 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Enzo</t>
+          <t>Tina</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fernandaz</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>Hedley</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>thedley@hotmail.com</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -703,15 +743,19 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jim</t>
+          <t>Aifor</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>Mendez</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>aiforvmendez@gmail.com</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -721,15 +765,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Hannah</t>
+          <t>Anne</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>Bowen</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>dereckanne@rogers.com</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -739,15 +787,19 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Drake</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>Yang</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>yang.julie519@yahoo.com</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -757,12 +809,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Savitra</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sapre</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -775,16 +827,3720 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Blake</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Russell</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Samantha</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Bernard</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>bernard@pickleplexclub.ca</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Wes</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cline</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>wcline57@gmail.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Shauna</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Fudge</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>sfudge11@outlook.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>asaf</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>misaljevic</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>asafmisa@rogers.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fineas</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Haw</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>McCaig</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>pmccaig@paulsan.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Carly</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Connor</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>carly.forsythe.connor@gmail.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Anna Laine</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Williams</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Yeshe</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Williams</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Lewis</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Jadea</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Collin</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Tyrese</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Collin</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Sunny</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Mattu</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>matsunny@gmail.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Enzo</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Fernandaz</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Jim</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Hannah</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Emily</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Drake</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Savitra</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sapre</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Riley</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Russell</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Eliana</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Dionisio</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Rodriguez</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>maria@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Brouwer</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Clark</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>wclark@northwestrubber.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Birkley</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Swan (Birka)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Omar</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Herzallah</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>omar.herzallah2003@gmail.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Bylsma</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Vornbrock</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Hrudik</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Mullapudi</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Vornbrock</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>KEVIN</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>VAISHNAV</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>kevin1122va@gmail.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Abby</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Caskie</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Celine</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Prygiel</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Bianca</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Prygiel</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Dominic</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ryan.dominic@pickleplex.ca</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Natalie</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Bodor</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>natalie@cglfinancial.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Sreesarani</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Mullapudi</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Ayaan</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Bhargava</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Vivaan</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Bhargava</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>devon</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>abbey</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>devon_abbey@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Fidel</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Chua</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>fidelchuajr@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Ruby</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Armes</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>rubyarmes2011@gmail.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Isabella</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Zolli</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>isabellazolli@cloud.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Danielle</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Fletcher</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>danielleannfletcher@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Kate</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Connor</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>geoffy91@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>wetherup</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>wetherup@execulink.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Jagjot</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Shergill</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>jagjotshergill2@gmail.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Natalie</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Dubuc</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>nataliedubuc@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Marlene</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Davis</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>mardavis1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Holly</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Bozzer-Cole</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>hollyleebc@gmail.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Jill</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Berridge</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>jillberridge@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Paven</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Brar</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>pavenbrar13@gmail.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Kamaldeep</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Sidhu</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>kami87sid@gmail.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Banmeet</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Brar</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>banibrar73@gmail.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Carole</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Bedard</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>clb_88@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>King</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>steveking23@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Deana</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Kox</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>deanajkox@gmail.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Rachel</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Jaffer</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>rsloat77@gmail.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Beth</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>McAllister</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>beth.mcallister@bchsys.org</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Christine</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Dickson</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>thedickson550@gmail.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Edward</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>edwardf.salazar@gmail.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Karen</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>McLeod</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>mcleodkaren52@gmail.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Lennox</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Fallis</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Derek</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>deVries</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Anthony</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Gosse</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Rikayla</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Baldin</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Nunn</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>alnunn@gmail.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Kait</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Ayers</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Tanner</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Baldin</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Jerika</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>deVries</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Kalissa</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Baran</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>kalissabaran@gmail.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Doran</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>stevedoranwriter@gmail.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Susan</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Arfo</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>susanam6995@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Katya</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Uhlman</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>katyauhlman@live.ca</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Hitchon</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>4hitches33@gmail.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Nicole</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Coomber</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>nicolecoomber@outlook.com</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Rhys</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Pollock</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>rhyspollock21@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Hitchon</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>4hicthes33@gmail.com</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Maria Ignacia Joshi</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Liwat</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>mijliwat2@gmail.com</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Pawan</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Kaur</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>pawan62batth@gmail.com</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Vicki</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>gajijagwas70@gmail.com</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Patrick</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Bonnie</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Param</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Atwal</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>parminderatwal6@gmail.com</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Sang</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Tran</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>sangertran@gmail.com</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Doyle</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>doylebill@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Natalie</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Hopkins</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>nataliehopkins008@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Glowala</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>glowala@gmail.com</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Kawal</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Attwal</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>deepkawal20@gmail.com</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Cathy</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Money</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>cathylmoney@gmail.com</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Mary</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Noble</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>keepin_fit@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Molly</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Sangster</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>molly.sangster@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Anita</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Barker</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>jbmh21@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Preet</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Panchi</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>preetmatharu2311@gmail.com</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Money</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>sclsmoney@gmail.com</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Logan</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Money</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>logangmoney@gmail.com</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Lewis</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>lewis021990@gmail.com</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Owen</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Snyder</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>owenytsnyder@gmail.com</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Alexia</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Zographos</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>xavier</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>lester</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>xavierlester321@icloud.com</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Hayden</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Gault</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>haydenlgault@gmail.com</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Jane</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Keyes</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>jandjkeyes@gmail.com</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Shawn</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Corey</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Claudia</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Volpe</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>claudialvolpe@gmail.com</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Bernadette</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Tadena</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>detht@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Shanice</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Mcfarlane</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>alliemcfarlane@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Hope</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Mutete</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>hmutete@gmail.com</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Alexandria</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Ciftja</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>ally.almon96@gmail.com</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Doug</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Hitchon</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>dhitchon072@gmail.com</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Justin</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Browell</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>jbrowell84@gmail.com</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Weekes</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>weekes2723@gmail.com</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Eugene</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Ciftja</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>eugeneciftja@gmail.com</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Jake</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Procaccini</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>jake.pro7187@gmail.com</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Young</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>paulyoung@jhyoung.com</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Serina</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Ramphal</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>serinaramphal8@gmail.com</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Megan</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Amarelo</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>megan.amarelo81@gmail.com</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Joanne</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Gadawski</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>jgadawski@rogers.com</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Shawn</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Lalla</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>shawnlalla@gmail.com</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Batista</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>tistaminis@gmail.com</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Darlene</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Hewson</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>dgraham348@msn.com</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Dave</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Kielstra</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>dkielstra@gmail.com</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Monte</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>montedan99@gmail.com</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Calvin</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Hewson</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>hewson99@rogers.com</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Lauren</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Kielstra</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>lkielstra@qmed.ca</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Harshdeep</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Mangat</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>harshdeep.mangat@icloud.com</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>enes</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>medanhodzic</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>enesmedanhodzic@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Allan</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Njeru</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>sethestar@gmail.com</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Halayna</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Mont Richard</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>halaynamonty@gmail.com</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Welton</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Shea</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>wshea0810@gmail.com</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Catherine</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Bandura</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>catherine.bandura@gmail.com</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Istvan</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Gyorki</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>idgyorki@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Natasha</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Muriithi</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Olena</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Severyn</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>olena.severyn29@gmail.com</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Allan</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Muriithi</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Eric</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Njeru</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Jennifer</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Ndungu</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Jacob</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Macdonald</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>jacob24macdonald@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Karen</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Love</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>rob</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Perry</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>robperry368@gmail.com</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Carol Ann</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>McCaig</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>cmccaig@rogers.com</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Josh</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Simpson</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>joshawasimpson@gmail.com</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Rob</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Love</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>rwglove@gmail.com</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Gordy</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Singh</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>69fairviewinc@gmail.com</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Dana</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Bearinger</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>dana@azrootbar.com</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Johnny</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Arcia</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>chiconutts23@gmail.com</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Jhanvi</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Nimavat</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>jhanvi.nimavat@gmail.com</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Andriyanov</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>a.andriyanov1989@gmail.com</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Heather</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>La Vecchia</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>hlschott@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Corinna</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Olmstead</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>chrisandcorinna@mac.com</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Russell</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Yurick</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>russell.yurick@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Jon</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Biros</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>jonbiros@gmail.com</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Spencer</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Benoit</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>spencerm.benoit@outlook.com</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Cristine</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Misiak</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>cristinemisiak@gmail.com</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Tyler</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Hoover</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>hoovdad27@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Athena</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Hedley</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>athenahedley@gmail.com</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Theresa</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Kozak</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>theresa.kozak1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Payton</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Fennema</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Kamala</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Ganeson</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>kamala.cganeson@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Blayze</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Crawford</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>blayzecrawford14@gmail.com</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Abbey</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Ball</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>abbey-layne@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Hope</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Jennions</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>abbey-layne1@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>peter</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>pelaez</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>peterpelaez12@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Martin Dave</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Buenviaje</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>martin.buenviaje11@gmail.com</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Palka</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>fluke02@gmail.com</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Ann July</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Buenviaje</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>annjulylauret@gmail.com</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>joanne</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>pelaez</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>thepelaez2025@gmail.com</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>MacDonald</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>taylormacdonald@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Docherty</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>docherty_thomas@ymail.com</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Tricia</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Klunder</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>tricia_klunder@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Emmalea</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>emmaleamay9@gmail.com</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Liam</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>liamporter_27@icloud.com</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Braydan</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Weekes</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>tadenabernadette@gmail.com</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Jesse</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Silva</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>silva.jessem@gmail.com</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Christina</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Lam</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>christinalam1990@gmail.com</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Don</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Petrone</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>donald.petrone@gmail.com</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Elizabeth</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>etmartin08@gmail.com</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>McClelland</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>mcclelland.sv@gmail.com</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
         </is>

--- a/docs/downloads/Brantford.xlsx
+++ b/docs/downloads/Brantford.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -479,17 +479,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Christine</t>
+          <t>Lynda</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ellis</t>
+          <t>Locche</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>christelljd5@gmail.com</t>
+          <t>lynda.locche@gmail.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -501,17 +501,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bruna</t>
+          <t>Gennarino</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Muniz</t>
+          <t>Lamacchia</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>brunamuniz@hotmail.com</t>
+          <t>president@cmimri.ca</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -523,17 +523,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FRANCES</t>
+          <t>Christine</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Galvez</t>
+          <t>Ellis</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>flmgalvez@gmail.com</t>
+          <t>christelljd5@gmail.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -545,17 +545,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Bruna</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Muniz</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>richard@pickleplexclub.ca</t>
+          <t>brunamuniz@hotmail.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -567,17 +567,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Susan</t>
+          <t>patrick</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Miller</t>
+          <t>engelhart</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>samiller345s@gmail.com</t>
+          <t>triactorpat96@gmail.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -589,17 +589,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vince</t>
+          <t>FRANCES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Colanardi</t>
+          <t>Galvez</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>vincevince2929@hotmail.com</t>
+          <t>flmgalvez@gmail.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -611,15 +611,19 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Martin</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>richard@pickleplexclub.ca</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -629,15 +633,19 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Blake</t>
+          <t>Susan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Martin</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>Miller</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>samiller345s@gmail.com</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -647,15 +655,19 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Samantha</t>
+          <t>Vince</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Martin</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>Colanardi</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>vincevince2929@hotmail.com</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -665,19 +677,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bernard</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lee</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>bernard@pickleplexclub.ca</t>
-        </is>
-      </c>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -687,19 +695,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Blake</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>brantfordmgmt@pickleplex.ca</t>
-        </is>
-      </c>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -709,12 +713,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Fineas</t>
+          <t>Samantha</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Haw</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -727,17 +731,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brantford</t>
+          <t>Bernard</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pickleplex</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>brantford@pickleplex.ca</t>
+          <t>bernard@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -749,15 +753,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Anna Laine</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Williams</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>Purfurst</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>jpurfurst@gmail.com</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -767,15 +775,19 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Yeshe</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Williams</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>brantfordmgmt@pickleplex.ca</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -785,12 +797,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Fineas</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lewis</t>
+          <t>Haw</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -803,17 +815,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ralph</t>
+          <t>Brantford</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Miller</t>
+          <t>Pickleplex</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ralphmiller717@gmail.com</t>
+          <t>brantford@pickleplex.ca</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -825,12 +837,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jadea</t>
+          <t>Anna Laine</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Collin</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -843,12 +855,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tyrese</t>
+          <t>Yeshe</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Collin</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -861,19 +873,15 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sunny</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mattu</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>matsunny@gmail.com</t>
-        </is>
-      </c>
+          <t>Lewis</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -883,15 +891,19 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Enzo</t>
+          <t>Ralph</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fernandaz</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>Miller</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ralphmiller717@gmail.com</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -901,12 +913,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jim</t>
+          <t>Jadea</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Miles</t>
+          <t>Collin</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -919,12 +931,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Hannah</t>
+          <t>Tyrese</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Miles</t>
+          <t>Collin</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -937,15 +949,19 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Sunny</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Drake</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>Mattu</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>matsunny@gmail.com</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -955,19 +971,15 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Keisha</t>
+          <t>Enzo</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Francis</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>keishaforsythe@hotmail.com</t>
-        </is>
-      </c>
+          <t>Fernandaz</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -977,19 +989,15 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Carmen</t>
+          <t>Jim</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Arico</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>arico.cm@gmail.com</t>
-        </is>
-      </c>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -999,12 +1007,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Savitra</t>
+          <t>Hannah</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sapre</t>
+          <t>Miles</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -1017,12 +1025,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Emily</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Russell</t>
+          <t>Drake</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -1035,15 +1043,19 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Eliana</t>
+          <t>Keisha</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dionisio</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>Francis</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>keishaforsythe@hotmail.com</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1053,17 +1065,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Carmen</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Rodriguez</t>
+          <t>Arico</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>maria@yahoo.ca</t>
+          <t>arico.cm@gmail.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1075,12 +1087,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Savitra</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Brouwer</t>
+          <t>Sapre</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -1093,19 +1105,15 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Clark</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>wclark@northwestrubber.com</t>
-        </is>
-      </c>
+          <t>Russell</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1115,12 +1123,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Birkley</t>
+          <t>Eliana</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Swan (Birka)</t>
+          <t>Dionisio</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1133,17 +1141,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Carla</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Arsenault</t>
+          <t>Rodriguez</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>carlaarsenault14@gmail.com</t>
+          <t>maria@yahoo.ca</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1155,19 +1163,15 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nadine</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kelly</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>nadine@springss.ca</t>
-        </is>
-      </c>
+          <t>Brouwer</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1177,15 +1181,19 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>William</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bylsma</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>Clark</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>wclark@northwestrubber.com</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1195,19 +1203,15 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Tom</t>
+          <t>Birkley</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Hodgson</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>henleybobbie@gmail.com</t>
-        </is>
-      </c>
+          <t>Swan (Birka)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1217,17 +1221,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Carla</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Keen</t>
+          <t>Arsenault</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>jennkeen@live.com</t>
+          <t>carlaarsenault14@gmail.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1239,15 +1243,19 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nadine</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Vornbrock</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>Kelly</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>nadine@springss.ca</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1257,12 +1265,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Hrudik</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mullapudi</t>
+          <t>Bylsma</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -1275,15 +1283,19 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Tom</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Vornbrock</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>Hodgson</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>henleybobbie@gmail.com</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1293,17 +1305,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Menegaldo</t>
+          <t>Keen</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>slapshot1192@gmail.com</t>
+          <t>jennkeen@live.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1315,19 +1327,15 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Vicki</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Edward</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>v.edward@rogers.com</t>
-        </is>
-      </c>
+          <t>Vornbrock</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1337,19 +1345,15 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Liz</t>
+          <t>Hrudik</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lemaitre</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>lizlemaitre@gmail.com</t>
-        </is>
-      </c>
+          <t>Mullapudi</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1359,12 +1363,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Abby</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Caskie</t>
+          <t>Vornbrock</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1377,17 +1381,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mainse</t>
+          <t>Menegaldo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ronmainse@gmail.com</t>
+          <t>slapshot1192@gmail.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1399,15 +1403,19 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Celine</t>
+          <t>Vicki</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Prygiel</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>Edward</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>v.edward@rogers.com</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1417,15 +1425,19 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Bianca</t>
+          <t>Liz</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Prygiel</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>Lemaitre</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>lizlemaitre@gmail.com</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1435,19 +1447,15 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sang</t>
+          <t>Abby</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tran</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>tiffanyhelenecarver@gmail.com</t>
-        </is>
-      </c>
+          <t>Caskie</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1457,17 +1465,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Norm</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Hastie</t>
+          <t>Mainse</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>norm.hasty@gmail.com</t>
+          <t>ronmainse@gmail.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1479,19 +1487,15 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Natalie</t>
+          <t>Celine</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bodor</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>natalie@cglfinancial.com</t>
-        </is>
-      </c>
+          <t>Prygiel</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1501,19 +1505,15 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Bianca</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cabral</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>emmadawn@bell.net</t>
-        </is>
-      </c>
+          <t>Prygiel</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1523,17 +1523,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ross</t>
+          <t>Sang</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Tran</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ross@ideas2profit.ca</t>
+          <t>tiffanyhelenecarver@gmail.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1545,17 +1545,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>George</t>
+          <t>Norm</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cabral</t>
+          <t>Hastie</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>g_dog@bell.net</t>
+          <t>norm.hasty@gmail.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1567,17 +1567,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Naga</t>
+          <t>Natalie</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mullapudi</t>
+          <t>Bodor</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>nagasaijyothim@gmail.com</t>
+          <t>natalie@cglfinancial.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1589,15 +1589,19 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sreesarani</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mullapudi</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>Cabral</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>emmadawn@bell.net</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1607,15 +1611,19 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Ayaan</t>
+          <t>Ross</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bhargava</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>Blaine</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ross@ideas2profit.ca</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1625,15 +1633,19 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Vivaan</t>
+          <t>George</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bhargava</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>Cabral</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>g_dog@bell.net</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1643,17 +1655,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Beth</t>
+          <t>Naga</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>McAllister</t>
+          <t>Mullapudi</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>beth.mcallister@bchsys.org</t>
+          <t>nagasaijyothim@gmail.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1665,12 +1677,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Lennox</t>
+          <t>Sreesarani</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Fallis</t>
+          <t>Mullapudi</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1683,12 +1695,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Derek</t>
+          <t>Ayaan</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>deVries</t>
+          <t>Bhargava</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1701,12 +1713,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Vivaan</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Gosse</t>
+          <t>Bhargava</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1719,15 +1731,19 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Rikayla</t>
+          <t>Beth</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Baldin</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>McAllister</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>beth.mcallister@bchsys.org</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1737,12 +1753,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Kait</t>
+          <t>Lennox</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ayers</t>
+          <t>Fallis</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1755,12 +1771,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Tanner</t>
+          <t>Derek</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Baldin</t>
+          <t>deVries</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1773,12 +1789,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Jerika</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>deVries</t>
+          <t>Gosse</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1791,12 +1807,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t>Rikayla</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Bonnie</t>
+          <t>Baldin</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1809,12 +1825,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Alexia</t>
+          <t>Kait</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Zographos</t>
+          <t>Ayers</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1827,12 +1843,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Shawn</t>
+          <t>Tanner</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Corey</t>
+          <t>Baldin</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1845,12 +1861,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Natasha</t>
+          <t>Jerika</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Muriithi</t>
+          <t>deVries</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1863,12 +1879,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Allan</t>
+          <t>Patrick</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Muriithi</t>
+          <t>Bonnie</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1881,12 +1897,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>Alexia</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Njeru</t>
+          <t>Zographos</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1899,12 +1915,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Shawn</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ndungu</t>
+          <t>Corey</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1917,12 +1933,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Natasha</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t>Muriithi</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1935,19 +1951,15 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cristine</t>
+          <t>Allan</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Misiak</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>cristinemisiak@gmail.com</t>
-        </is>
-      </c>
+          <t>Muriithi</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1957,12 +1969,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Payton</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Fennema</t>
+          <t>Njeru</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1975,12 +1987,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Tarah</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Pennings</t>
+          <t>Ndungu</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1993,12 +2005,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Anika</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Walsh</t>
+          <t>Love</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -2011,15 +2023,19 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Kelsey</t>
+          <t>Cristine</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Pennings</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+          <t>Misiak</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>cristinemisiak@gmail.com</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2029,12 +2045,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Ellien</t>
+          <t>Payton</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Pennings</t>
+          <t>Fennema</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -2047,15 +2063,19 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Pennings</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
+          <t>Disher-Neddow</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>daireedelite@gmail.com</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2065,19 +2085,15 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>alexandria</t>
+          <t>Tarah</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>lex_street@hotmail.com</t>
-        </is>
-      </c>
+          <t>Pennings</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2087,16 +2103,1246 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Rajan</t>
+          <t>Anika</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Jain Chouhan</t>
+          <t>Walsh</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Kelsey</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Pennings</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Ellien</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Pennings</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Pennings</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>alexandria</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>street</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>lex_street@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Rajan</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Jain Chouhan</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Arunkumar</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>sujamol</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>arunjayakumarqlnv@gmail.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Darwan</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Wilsin</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>darrenwilsin46@gmail.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Arun</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>kv</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>arunvnu444@gmail.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Sunson</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>sunsonthomas10@gmail.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Wyatt</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Cook</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Demaya</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Jenkins</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>toptiertipss@gmail.com</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Marty</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Ditchburn</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>marty.ditchburn@gmail.com</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Anu</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Ajith</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>ananthuajith03@gmail.com</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Eleanor</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Vandenbrink</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ellie.vancasey@protonmail.com</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Joel</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>McKinnon</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>joeljmckinnon@gmail.com</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Amy</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>MacMillan</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>amy26mac@icloud.com</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>annalise</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>gadsby</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>annalisegadsby@gmail.com</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Derek</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Bravo</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>derek.wbravo@gmail.com</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Sophie</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Vandenbrink</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>sophie.vancasey@gmail.com</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>McManamy</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>mark.mcmanamy@gmail.com</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Gerald</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Shea</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>geraldshea1978@gmail.com</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Jen</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Bravo</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>jenbravo19@gmail.com</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Ryleigh</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Lofgren</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>ryleighstar@icloud.com</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>BETH</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>EKRON</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>beth.ekron@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Melanie</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Cabrera</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>red.raven07@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Priya</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Gita</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>sivapriyag541@gmail.com</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Jeff</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Hedley</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>jeff74hedley@gmail.com</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Jaykumar</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Patel</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>pateljayd97@gmail.com</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Jessica</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Rattle</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>jessrattle@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Jessica</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Poos</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>jesspoos@gmail.com</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Lewis</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>kristencar@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Poos</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>kevindpoos@gmail.com</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Katrina</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Dalton</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>katrinadalton3@gmail.com</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Jeanette</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Carnegie</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>jcarnegie5@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Mason</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>shannelly</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ISABELLA</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>PAIXAO</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>bellapaixao80@gmail.com</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Poos</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>jpoos297@gmail.com</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Mary ann</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Laughlin</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>mshannc614@rogers.com</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Audrey</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Belanger</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>bell.audrey@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Farzaana</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Coovadia</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>farzaana.coovadia@gmail.com</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Evans</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>uturntimmy@gmail.com</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Angel</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Evans</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>tjagevans@gmail.com</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Sharon</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Rideout</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>skrideout@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Crosby</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Gibson</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>crosby.gibson@rogers.com</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Cole</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Armitaje</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>cole_armatje@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Evan</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Engell</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>evan@northshore.tax</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>antoinette</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>providence</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>aprovidedh8@gmail.com</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Zefferino</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>fzeffer@gmail.com</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Lynn</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Joshi</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>lynn54099@gmail.com</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Will</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Jansen</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>wjansen1919@gmail.com</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Tom</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Engell</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>tomengell@outlook.com</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Laurie</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Zefferino</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>l.zefferino@gmail.com</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Morton</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>mattmorton91@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Izzy</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Fortier</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>fortierizzy@icloud.com</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Rideout</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>emma.rideout@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Davis</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Wylie</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>dwylie793@gmail.com</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Jim</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Peitro</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>gym.peitro@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
         </is>

--- a/docs/downloads/Brantford.xlsx
+++ b/docs/downloads/Brantford.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D142"/>
+  <dimension ref="A1:D143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -815,12 +815,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Pickleplex</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>Brantford</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Pickleplex</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3343,6 +3343,28 @@
         </is>
       </c>
       <c r="D142" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Olmstead</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>ljolms@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
         </is>

--- a/docs/downloads/Brantford.xlsx
+++ b/docs/downloads/Brantford.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D143"/>
+  <dimension ref="A1:D213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -523,17 +523,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Christine</t>
+          <t>Darryl</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ellis</t>
+          <t>Burtch</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>christelljd5@gmail.com</t>
+          <t>darryl.burtch@me.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -545,17 +545,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bruna</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Muniz</t>
+          <t>Martz</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>brunamuniz@hotmail.com</t>
+          <t>sparkees66@gmail.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -567,17 +567,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>patrick</t>
+          <t>Bruna</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>engelhart</t>
+          <t>Muniz</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>triactorpat96@gmail.com</t>
+          <t>brunamuniz@hotmail.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -589,17 +589,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FRANCES</t>
+          <t>patrick</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Galvez</t>
+          <t>engelhart</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>flmgalvez@gmail.com</t>
+          <t>triactorpat96@gmail.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -611,17 +611,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>FRANCES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Galvez</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>richard@pickleplexclub.ca</t>
+          <t>flmgalvez@gmail.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -633,17 +633,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Susan</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Miller</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>samiller345s@gmail.com</t>
+          <t>richard@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -655,17 +655,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Vince</t>
+          <t>Susan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Colanardi</t>
+          <t>Miller</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>vincevince2929@hotmail.com</t>
+          <t>samiller345s@gmail.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -815,17 +815,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pickleplex</t>
+          <t>Saad</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Brantford</t>
+          <t>Daqar</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>brantford@pickleplex.ca</t>
+          <t>saad_dq@yahoo.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -837,15 +837,19 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Anna Laine</t>
+          <t>Pickleplex</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Williams</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>Brantford</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -855,7 +859,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Yeshe</t>
+          <t>Anna Laine</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -873,12 +877,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Yeshe</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lewis</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -891,19 +895,15 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ralph</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Miller</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>ralphmiller717@gmail.com</t>
-        </is>
-      </c>
+          <t>Lewis</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -913,15 +913,19 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jadea</t>
+          <t>Ralph</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Collin</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>Miller</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ralphmiller717@gmail.com</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -931,7 +935,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tyrese</t>
+          <t>Jadea</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -949,19 +953,15 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sunny</t>
+          <t>Tyrese</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mattu</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>matsunny@gmail.com</t>
-        </is>
-      </c>
+          <t>Collin</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -971,15 +971,19 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Enzo</t>
+          <t>Sunny</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fernandaz</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>Mattu</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>matsunny@gmail.com</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -989,12 +993,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Jim</t>
+          <t>Enzo</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Miles</t>
+          <t>Fernandaz</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -1007,7 +1011,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hannah</t>
+          <t>Jim</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1025,12 +1029,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Hannah</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Drake</t>
+          <t>Miles</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -1043,19 +1047,15 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Keisha</t>
+          <t>Emily</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Francis</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>keishaforsythe@hotmail.com</t>
-        </is>
-      </c>
+          <t>Drake</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1065,17 +1065,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Carmen</t>
+          <t>Keisha</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Arico</t>
+          <t>Francis</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>arico.cm@gmail.com</t>
+          <t>keishaforsythe@hotmail.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1087,15 +1087,19 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Savitra</t>
+          <t>Carmen</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sapre</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>Arico</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>arico.cm@gmail.com</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1105,12 +1109,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Savitra</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Russell</t>
+          <t>Sapre</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -1123,12 +1127,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Eliana</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dionisio</t>
+          <t>Russell</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1141,19 +1145,15 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Eliana</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Rodriguez</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>maria@yahoo.ca</t>
-        </is>
-      </c>
+          <t>Dionisio</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1163,15 +1163,19 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Brouwer</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>Rodriguez</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>maria@yahoo.ca</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1181,19 +1185,15 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Clark</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>wclark@northwestrubber.com</t>
-        </is>
-      </c>
+          <t>Brouwer</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1203,15 +1203,19 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Birkley</t>
+          <t>William</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Swan (Birka)</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>Clark</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>wclark@northwestrubber.com</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1221,19 +1225,15 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Carla</t>
+          <t>Birkley</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Arsenault</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>carlaarsenault14@gmail.com</t>
-        </is>
-      </c>
+          <t>Swan (Birka)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1243,17 +1243,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Nadine</t>
+          <t>Carla</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Arsenault</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>nadine@springss.ca</t>
+          <t>carlaarsenault14@gmail.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1265,15 +1265,19 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Nadine</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bylsma</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>Kelly</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>nadine@springss.ca</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1283,19 +1287,15 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Tom</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Hodgson</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>henleybobbie@gmail.com</t>
-        </is>
-      </c>
+          <t>Bylsma</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1305,17 +1305,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Tom</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Keen</t>
+          <t>Hodgson</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>jennkeen@live.com</t>
+          <t>henleybobbie@gmail.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1327,15 +1327,19 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Vornbrock</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>Keen</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>jennkeen@live.com</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1345,12 +1349,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Hrudik</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mullapudi</t>
+          <t>Vornbrock</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1363,12 +1367,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Hrudik</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Vornbrock</t>
+          <t>Mullapudi</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1381,19 +1385,15 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Menegaldo</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>slapshot1192@gmail.com</t>
-        </is>
-      </c>
+          <t>Vornbrock</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1403,17 +1403,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Vicki</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Menegaldo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>v.edward@rogers.com</t>
+          <t>slapshot1192@gmail.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1425,17 +1425,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Liz</t>
+          <t>Vicki</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Lemaitre</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>lizlemaitre@gmail.com</t>
+          <t>v.edward@rogers.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1447,15 +1447,19 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Abby</t>
+          <t>Liz</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Caskie</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>Lemaitre</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>lizlemaitre@gmail.com</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1465,19 +1469,15 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Abby</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mainse</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>ronmainse@gmail.com</t>
-        </is>
-      </c>
+          <t>Caskie</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1487,15 +1487,19 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Celine</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Prygiel</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>Mainse</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ronmainse@gmail.com</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1505,7 +1509,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bianca</t>
+          <t>Celine</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1523,19 +1527,15 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sang</t>
+          <t>Bianca</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tran</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>tiffanyhelenecarver@gmail.com</t>
-        </is>
-      </c>
+          <t>Prygiel</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1545,17 +1545,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Norm</t>
+          <t>Sang</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Hastie</t>
+          <t>Tran</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>norm.hasty@gmail.com</t>
+          <t>tiffanyhelenecarver@gmail.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1567,17 +1567,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Natalie</t>
+          <t>Norm</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bodor</t>
+          <t>Hastie</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>natalie@cglfinancial.com</t>
+          <t>norm.hasty@gmail.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1589,17 +1589,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Natalie</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cabral</t>
+          <t>Bodor</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>emmadawn@bell.net</t>
+          <t>natalie@cglfinancial.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1611,17 +1611,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Ross</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Cabral</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ross@ideas2profit.ca</t>
+          <t>emmadawn@bell.net</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1633,17 +1633,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>George</t>
+          <t>Ross</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cabral</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>g_dog@bell.net</t>
+          <t>ross@ideas2profit.ca</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1655,17 +1655,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Naga</t>
+          <t>George</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mullapudi</t>
+          <t>Cabral</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>nagasaijyothim@gmail.com</t>
+          <t>g_dog@bell.net</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1677,7 +1677,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sreesarani</t>
+          <t>Naga</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1685,7 +1685,11 @@
           <t>Mullapudi</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>nagasaijyothim@gmail.com</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1695,12 +1699,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ayaan</t>
+          <t>Sreesarani</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Bhargava</t>
+          <t>Mullapudi</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1713,7 +1717,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Vivaan</t>
+          <t>Ayaan</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1731,19 +1735,15 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Beth</t>
+          <t>Vivaan</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>McAllister</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>beth.mcallister@bchsys.org</t>
-        </is>
-      </c>
+          <t>Bhargava</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1753,15 +1753,19 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Lennox</t>
+          <t>Beth</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Fallis</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>McAllister</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>beth.mcallister@bchsys.org</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1771,15 +1775,19 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Derek</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>deVries</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>Chan</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>gregc@pickleplex.ca</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1789,12 +1797,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Lennox</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Gosse</t>
+          <t>Fallis</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1807,12 +1815,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Rikayla</t>
+          <t>Derek</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Baldin</t>
+          <t>deVries</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1825,12 +1833,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Kait</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ayers</t>
+          <t>Gosse</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1843,7 +1851,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Tanner</t>
+          <t>Rikayla</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1861,12 +1869,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Jerika</t>
+          <t>Kait</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>deVries</t>
+          <t>Ayers</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1879,12 +1887,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t>Tanner</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bonnie</t>
+          <t>Baldin</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1897,12 +1905,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Alexia</t>
+          <t>Jerika</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Zographos</t>
+          <t>deVries</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1915,12 +1923,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Shawn</t>
+          <t>Patrick</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Corey</t>
+          <t>Bonnie</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1933,12 +1941,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Natasha</t>
+          <t>Alexia</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Muriithi</t>
+          <t>Zographos</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1951,12 +1959,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Allan</t>
+          <t>Shawn</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Muriithi</t>
+          <t>Corey</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1969,12 +1977,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>Natasha</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Njeru</t>
+          <t>Muriithi</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1987,12 +1995,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Allan</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ndungu</t>
+          <t>Muriithi</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -2005,12 +2013,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t>Njeru</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -2023,19 +2031,15 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cristine</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Misiak</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>cristinemisiak@gmail.com</t>
-        </is>
-      </c>
+          <t>Ndungu</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2045,12 +2049,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Payton</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Fennema</t>
+          <t>Love</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -2063,17 +2067,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Cristine</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Disher-Neddow</t>
+          <t>Misiak</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>daireedelite@gmail.com</t>
+          <t>cristinemisiak@gmail.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2085,12 +2089,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Tarah</t>
+          <t>Payton</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pennings</t>
+          <t>Fennema</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -2103,15 +2107,19 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Anika</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Walsh</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr"/>
+          <t>Disher-Neddow</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>daireedelite@gmail.com</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2121,7 +2129,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Kelsey</t>
+          <t>Tarah</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2139,12 +2147,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Ellien</t>
+          <t>Anika</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Pennings</t>
+          <t>Walsh</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -2157,7 +2165,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Kelsey</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2175,19 +2183,15 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>alexandria</t>
+          <t>Ellien</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>lex_street@hotmail.com</t>
-        </is>
-      </c>
+          <t>Pennings</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2197,12 +2201,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Rajan</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Jain Chouhan</t>
+          <t>Pennings</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -2215,17 +2219,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Arunkumar</t>
+          <t>alexandria</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>sujamol</t>
+          <t>street</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>arunjayakumarqlnv@gmail.com</t>
+          <t>lex_street@hotmail.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2237,19 +2241,15 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Darwan</t>
+          <t>Rajan</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Wilsin</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>darrenwilsin46@gmail.com</t>
-        </is>
-      </c>
+          <t>Jain Chouhan</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2259,17 +2259,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Arun</t>
+          <t>Arunkumar</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>kv</t>
+          <t>sujamol</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>arunvnu444@gmail.com</t>
+          <t>arunjayakumarqlnv@gmail.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2281,17 +2281,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sunson</t>
+          <t>Darwan</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Wilsin</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>sunsonthomas10@gmail.com</t>
+          <t>darrenwilsin46@gmail.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2303,15 +2303,19 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Wyatt</t>
+          <t>Arun</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cook</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr"/>
+          <t>kv</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>arunvnu444@gmail.com</t>
+        </is>
+      </c>
       <c r="D95" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2321,17 +2325,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Demaya</t>
+          <t>Sunson</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Jenkins</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>toptiertipss@gmail.com</t>
+          <t>sunsonthomas10@gmail.com</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2343,19 +2347,15 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Marty</t>
+          <t>Wyatt</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ditchburn</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>marty.ditchburn@gmail.com</t>
-        </is>
-      </c>
+          <t>Cook</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2365,17 +2365,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Anu</t>
+          <t>Demaya</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ajith</t>
+          <t>Jenkins</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ananthuajith03@gmail.com</t>
+          <t>toptiertipss@gmail.com</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2387,17 +2387,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Eleanor</t>
+          <t>Marty</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Vandenbrink</t>
+          <t>Ditchburn</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ellie.vancasey@protonmail.com</t>
+          <t>marty.ditchburn@gmail.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2409,17 +2409,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Joel</t>
+          <t>Anu</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>McKinnon</t>
+          <t>Ajith</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>joeljmckinnon@gmail.com</t>
+          <t>ananthuajith03@gmail.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2431,17 +2431,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Amy</t>
+          <t>Eleanor</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MacMillan</t>
+          <t>Vandenbrink</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>amy26mac@icloud.com</t>
+          <t>ellie.vancasey@protonmail.com</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2453,17 +2453,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>annalise</t>
+          <t>Joel</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>gadsby</t>
+          <t>McKinnon</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>annalisegadsby@gmail.com</t>
+          <t>joeljmckinnon@gmail.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2475,17 +2475,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Derek</t>
+          <t>Amy</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>MacMillan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>derek.wbravo@gmail.com</t>
+          <t>amy26mac@icloud.com</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2497,17 +2497,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sophie</t>
+          <t>annalise</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Vandenbrink</t>
+          <t>gadsby</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>sophie.vancasey@gmail.com</t>
+          <t>annalisegadsby@gmail.com</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2519,17 +2519,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Derek</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>McManamy</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>mark.mcmanamy@gmail.com</t>
+          <t>derek.wbravo@gmail.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2541,17 +2541,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Gerald</t>
+          <t>Sophie</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Shea</t>
+          <t>Vandenbrink</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>geraldshea1978@gmail.com</t>
+          <t>sophie.vancasey@gmail.com</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2563,17 +2563,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Jen</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>McManamy</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>jenbravo19@gmail.com</t>
+          <t>mark.mcmanamy@gmail.com</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2585,17 +2585,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Ryleigh</t>
+          <t>Gerald</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Lofgren</t>
+          <t>Shea</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ryleighstar@icloud.com</t>
+          <t>geraldshea1978@gmail.com</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2607,17 +2607,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BETH</t>
+          <t>Jen</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>EKRON</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>beth.ekron@hotmail.com</t>
+          <t>jenbravo19@gmail.com</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2629,17 +2629,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Melanie</t>
+          <t>Ryleigh</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Lofgren</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>red.raven07@yahoo.com</t>
+          <t>ryleighstar@icloud.com</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2651,17 +2651,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Priya</t>
+          <t>BETH</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Gita</t>
+          <t>EKRON</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>sivapriyag541@gmail.com</t>
+          <t>beth.ekron@hotmail.com</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2673,17 +2673,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Jeff</t>
+          <t>Melanie</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>jeff74hedley@gmail.com</t>
+          <t>red.raven07@yahoo.com</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2695,17 +2695,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Jaykumar</t>
+          <t>Priya</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Gita</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>pateljayd97@gmail.com</t>
+          <t>sivapriyag541@gmail.com</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -2717,17 +2717,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>Jaykumar</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Rattle</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>jessrattle@hotmail.com</t>
+          <t>pateljayd97@gmail.com</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Poos</t>
+          <t>Rattle</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>jesspoos@gmail.com</t>
+          <t>jessrattle@hotmail.com</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -2761,17 +2761,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Kristen</t>
+          <t>Jessica</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Lewis</t>
+          <t>Poos</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>kristencar@hotmail.com</t>
+          <t>jesspoos@gmail.com</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -2783,17 +2783,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Kristen</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Poos</t>
+          <t>Lewis</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>kevindpoos@gmail.com</t>
+          <t>kristencar@hotmail.com</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -2805,17 +2805,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Katrina</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Dalton</t>
+          <t>Poos</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>katrinadalton3@gmail.com</t>
+          <t>kevindpoos@gmail.com</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -2827,17 +2827,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Jeanette</t>
+          <t>Katrina</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Carnegie</t>
+          <t>Dalton</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>jcarnegie5@hotmail.com</t>
+          <t>katrinadalton3@gmail.com</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -2849,15 +2849,19 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>Jeanette</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>shannelly</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>Carnegie</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>jcarnegie5@hotmail.com</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2867,19 +2871,15 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ISABELLA</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PAIXAO</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>bellapaixao80@gmail.com</t>
-        </is>
-      </c>
+          <t>shannelly</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2889,17 +2889,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>ISABELLA</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Poos</t>
+          <t>PAIXAO</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>jpoos297@gmail.com</t>
+          <t>bellapaixao80@gmail.com</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -2911,17 +2911,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Mary ann</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Laughlin</t>
+          <t>Poos</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>mshannc614@rogers.com</t>
+          <t>jpoos297@gmail.com</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -2933,17 +2933,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Mary ann</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Belanger</t>
+          <t>Laughlin</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>bell.audrey@hotmail.com</t>
+          <t>mshannc614@rogers.com</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -2955,17 +2955,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Farzaana</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Coovadia</t>
+          <t>Belanger</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>farzaana.coovadia@gmail.com</t>
+          <t>bell.audrey@hotmail.com</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -2977,17 +2977,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Farzaana</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Evans</t>
+          <t>Coovadia</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>uturntimmy@gmail.com</t>
+          <t>farzaana.coovadia@gmail.com</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -2999,7 +2999,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Angel</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>tjagevans@gmail.com</t>
+          <t>uturntimmy@gmail.com</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3021,17 +3021,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sharon</t>
+          <t>Angel</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Rideout</t>
+          <t>Evans</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>skrideout@yahoo.ca</t>
+          <t>tjagevans@gmail.com</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3043,17 +3043,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Crosby</t>
+          <t>Sharon</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Gibson</t>
+          <t>Rideout</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>crosby.gibson@rogers.com</t>
+          <t>skrideout@yahoo.ca</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3351,20 +3351,1512 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
+          <t>Amanda</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Roorda</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>amanda.roorda@gmail.com</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
           <t>Lorena</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>Olmstead</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>ljolms@hotmail.com</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Knox</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Morton</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Jane</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Horney</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>hazelnjh7@gmail.com</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Johnson</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>adamr.sr.84@gmail.com</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Cheri</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Ruprai</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>cbeaton99@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Anderson</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>thegang110@gmail.com</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Tammy</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Davis</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>tjddavis71@gmail.com</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Kendall</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Morton</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Jessica</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Morton</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Gord</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Bryenton</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>rosebryenton@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Natalie</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Hein</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>nataliehein05@gmail.com</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Campbell</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>MacKinnon</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>campbelljamesmackinnon@gmail.com</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Tori</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Sitwell</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>tori_stiwell@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Brandy</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Spence</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>gbspence@rogers.com</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Greg</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Spence</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>gbspence@gmail.com</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Todd</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>McPherson</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>todd_mcp@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Isabel</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Simmons</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>isabel.simmons@icloud.com</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Jake</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>jacobw.paul@outlook.com</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>karina</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>morrison</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>karinaditchburn21@gmail.com</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>alicia</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>ditchburn</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>aliciaditchburn51@gmail.com</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Slattery</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>david.slattery@outlook.com</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Connor</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Crickmore</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>connor.crickmore@icloud.com</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>amy</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>ditchburn</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>amy.ditchburn54@gmail.com</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Ashton</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Welsh</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>ashtoncwelsh@gmail.com</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Cam</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Welsh</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>cameronmwelsh@gmail.com</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>wesley</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>bramham</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>cameronmatthewwelsh@gmail.com</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Hadeer</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Dawood</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>hadeerdawoodd@icloud.com</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Arunkumar</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Jayakumar Sujamol</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>arunjayakumarqlnd@gmail.com</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Lowther</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Joyce</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Sage</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>joyce_sage@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Émilie-Céline</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Lowther</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>drgnflysmith@gmail.com</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Areej</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Naseer</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Trevor</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>sales.bowmanville@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Simon</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Gonzalez</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>simon.gonzalez.n@icloud.com</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Wania</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Ashfaq</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>sadafsaki786@gmail.com</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Sheryl</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Van Kruistum</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>savk1096@gmail.com</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Gonzalez</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>pablogonar2004@icloud.com</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Fatema</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Alashmouti</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>fatima_ashmouti@icloud.com</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Garett</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Korber</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>sgkorber@sympatico.ca</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Emaan</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Daud</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>emaandaud504@icloud.com</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Fatima</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Safdar</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Nikki</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Nuun</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>nikkinuun@msn.com</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Dua</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Safdar</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Lateefah</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Binuyo</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>lateefahbinuyo@gmail.com</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Julieta</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Narvaez</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>narvaezjulieta@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Zainab</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Naseer</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>naseerzainab85@gmail.com</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Farzana</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Kausar</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>farzanakausar25@gmail.com</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Caisha</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Nuun</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Durrah</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Adil</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>durrah869@gmail.com</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Karida</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Ansary</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>taj.nesa@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Van Kruistum</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>tavk1081@gmail.com</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Hodan</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Nuun</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>rachel</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>bryant</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>rachelbryant838@gmail.com</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Elaine</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Hazlett</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>thehazletts@rogers.com</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>arwa</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>rostom</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>arwarostom13@gmail.com</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>zeliha</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>demir</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>zelihad696@gmail.com</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Lamar</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Dawood</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>ruqaya.ahmed22@gmail.com</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Ghazal</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Alashmouti</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>galashmouti@icloud.com</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Aiza</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Tayyeb</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>aiza14tayyeb@gmail.com</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Merza</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>s.mrza.1504@gmail.com</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Andres</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Gonzalez</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>afgon@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Zaynah</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Molani</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>zaynahmolani@gmail.com</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Robina</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Rafique</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>robina.rafique@gmail.com</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Manal</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Naseer</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Kendall</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Morton</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Salicia</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Postam</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>saliciap48@gmail.com</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Donna</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Hood</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>hoodd@rogers.com</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>klm.austin@cogeco.ca</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Jessica</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Morton</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>jessicahead@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Knox</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Morton</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
         </is>

--- a/docs/downloads/Brantford.xlsx
+++ b/docs/downloads/Brantford.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D213"/>
+  <dimension ref="A1:D366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -457,12 +457,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>TEST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gauvreau</t>
+          <t>TEST</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -479,17 +479,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lynda</t>
+          <t>Barb</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Locche</t>
+          <t>Erhardt</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>lynda.locche@gmail.com</t>
+          <t>demaambe@gmail.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -501,17 +501,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gennarino</t>
+          <t>serena</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lamacchia</t>
+          <t>mendizabal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>president@cmimri.ca</t>
+          <t>renamendiza@gmail.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -523,17 +523,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Darryl</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Burtch</t>
+          <t>Hicks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>darryl.burtch@me.com</t>
+          <t>hicksychef@hotmail.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -545,17 +545,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Jerrica</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Martz</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sparkees66@gmail.com</t>
+          <t>jerrlynnemarion@hotmail.ca</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -567,17 +567,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bruna</t>
+          <t>Alicia</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Muniz</t>
+          <t>Melady</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>brunamuniz@hotmail.com</t>
+          <t>aliciamelady@gmail.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -589,17 +589,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>patrick</t>
+          <t>Niyati</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>engelhart</t>
+          <t>Modi</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>triactorpat96@gmail.com</t>
+          <t>niyatimodi107@gmail.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -611,17 +611,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FRANCES</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Galvez</t>
+          <t>Schilter</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>flmgalvez@gmail.com</t>
+          <t>kimschilter789@gmail.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -633,17 +633,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Bob</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Mattice</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>richard@pickleplexclub.ca</t>
+          <t>bobmattice1964@gmail.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -655,17 +655,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Susan</t>
+          <t>Heather</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Miller</t>
+          <t>McDaniel</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>samiller345s@gmail.com</t>
+          <t>heathermcd.hm@gmail.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -677,15 +677,19 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Lynda</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Martin</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>Locche</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>lynda.locche@gmail.com</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -695,15 +699,19 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Blake</t>
+          <t>Gennarino</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Martin</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>Lamacchia</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>president@cmimri.ca</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -713,15 +721,19 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Samantha</t>
+          <t>Darryl</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Martin</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>Burtch</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>darryl.burtch@me.com</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -731,17 +743,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bernard</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Martz</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>bernard@pickleplexclub.ca</t>
+          <t>sparkees66@gmail.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -753,17 +765,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>patrick</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Purfurst</t>
+          <t>engelhart</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>jpurfurst@gmail.com</t>
+          <t>triactorpat96@gmail.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -775,17 +787,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>FRANCES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Galvez</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>brantfordmgmt@pickleplex.ca</t>
+          <t>flmgalvez@gmail.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -797,15 +809,19 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Fineas</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Haw</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>richard@pickleplexclub.ca</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -815,17 +831,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Saad</t>
+          <t>Susan</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Daqar</t>
+          <t>Miller</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>saad_dq@yahoo.com</t>
+          <t>samiller345s@gmail.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -837,17 +853,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pickleplex</t>
+          <t>Landon</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Brantford</t>
+          <t>Bursey</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>brantford@pickleplex.ca</t>
+          <t>landon.b@hotmail.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -859,15 +875,19 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Anna Laine</t>
+          <t>Lesley</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Williams</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>adeptofiat@gmail.com</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -877,15 +897,19 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Yeshe</t>
+          <t>Evelina</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Williams</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>Palka</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gapka03@gmail.com</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -895,15 +919,19 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lewis</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>Hewitson</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>victoriahewitson@gmail.com</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -913,17 +941,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ralph</t>
+          <t>Jill</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Miller</t>
+          <t>Hohs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ralphmiller717@gmail.com</t>
+          <t>jillhohs@hotmail.ca</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -935,15 +963,19 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jadea</t>
+          <t>Darren</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Collin</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>Richarz</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>dricharz@hotmail.com</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -953,15 +985,19 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Tyrese</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Collin</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>Mitchell</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>pmitchell44@rogers.com</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -971,17 +1007,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sunny</t>
+          <t>Emmalyn</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mattu</t>
+          <t>Busch</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>matsunny@gmail.com</t>
+          <t>emmalynsaint@yahoo.ca</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -993,15 +1029,19 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Enzo</t>
+          <t>Hunter</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fernandaz</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>Ballantyne</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>hunterballantyne9@gmail.com</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1011,15 +1051,19 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jim</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>Mitchell</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>m.es.mitchell@gmail.com</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1029,15 +1073,19 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hannah</t>
+          <t>Pam</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>Skidmore</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>pamskidmore015@gmail.com</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1047,15 +1095,19 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Tracey</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Drake</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>Taylor-O'Reilly</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>tracey.tor@gmail.com</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1065,17 +1117,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Keisha</t>
+          <t>Sam</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Francis</t>
+          <t>Jeavons</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>keishaforsythe@hotmail.com</t>
+          <t>samjeavv@gmail.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1087,17 +1139,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Carmen</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Arico</t>
+          <t>Gernhart</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>arico.cm@gmail.com</t>
+          <t>dagernhart@sympatico.ca</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1109,15 +1161,19 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Savitra</t>
+          <t>Jenn</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sapre</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>Bathgate</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>jennbathgate@gmail.com</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1127,15 +1183,19 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Russell</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>Finkelstein</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>em.finkelstein4212@gmail.com</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1145,15 +1205,19 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Eliana</t>
+          <t>Alana</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Dionisio</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>McDonald</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>alanamcdonald150@gmail.com</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1163,17 +1227,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Samantha</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Rodriguez</t>
+          <t>Spray</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>maria@yahoo.ca</t>
+          <t>samanaspray@icloud.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1185,15 +1249,19 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Joyce</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Brouwer</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>Sage</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>joyce_ssge@hotmail.com</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1203,17 +1271,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Laurie</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Clark</t>
+          <t>Shipp</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>wclark@northwestrubber.com</t>
+          <t>laurieshipp@hotmail.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1225,15 +1293,19 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Birkley</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Swan (Birka)</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>Wiepjes</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ttayloralexanderr@gmail.com</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1243,19 +1315,15 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Carla</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Arsenault</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>carlaarsenault14@gmail.com</t>
-        </is>
-      </c>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1265,19 +1333,15 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Nadine</t>
+          <t>Blake</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kelly</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>nadine@springss.ca</t>
-        </is>
-      </c>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1287,12 +1351,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Samantha</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bylsma</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -1305,17 +1369,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Tom</t>
+          <t>Bernard</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hodgson</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>henleybobbie@gmail.com</t>
+          <t>bernard@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1332,12 +1396,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Keen</t>
+          <t>Purfurst</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jennkeen@live.com</t>
+          <t>jpurfurst@gmail.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1349,15 +1413,19 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Denise</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Vornbrock</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>Holland</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>nieceden@hotmail.com</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1367,15 +1435,19 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Hrudik</t>
+          <t>Satinder</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mullapudi</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>Gill</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>satinder.11@hotmail.com</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1385,15 +1457,19 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Mauro</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Vornbrock</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>Evangelista</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>m.evangelista01@gmail.com</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1403,17 +1479,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Francesca</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Menegaldo</t>
+          <t>Carrieri</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>slapshot1192@gmail.com</t>
+          <t>carrieri_fran21@hotmail.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1425,17 +1501,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Vicki</t>
+          <t>Bev</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Hoekman</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>v.edward@rogers.com</t>
+          <t>bookloverbh@hotmail.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1447,17 +1523,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Liz</t>
+          <t>Kyia</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Lemaitre</t>
+          <t>Chopiak</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>lizlemaitre@gmail.com</t>
+          <t>chopiakk@gmail.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1469,15 +1545,19 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Abby</t>
+          <t>Ruth</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Caskie</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>Wain</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>mrs.ruth.wain@gmail.com</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1487,17 +1567,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mainse</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ronmainse@gmail.com</t>
+          <t>brantfordmgmt@pickleplex.ca</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1509,15 +1589,19 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Celine</t>
+          <t>Cindy</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Prygiel</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>Bes</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>jbes@rogers.com</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1527,15 +1611,19 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Bianca</t>
+          <t>Hiral</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Prygiel</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>Patel</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>hiralpatel6337@gmail.com</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1545,17 +1633,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sang</t>
+          <t>Heather</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tran</t>
+          <t>Maxwell</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>tiffanyhelenecarver@gmail.com</t>
+          <t>heather@maxwellmanagementgroup.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1567,19 +1655,15 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Norm</t>
+          <t>Fineas</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Hastie</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>norm.hasty@gmail.com</t>
-        </is>
-      </c>
+          <t>Haw</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1589,17 +1673,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Natalie</t>
+          <t>Shaelyn</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bodor</t>
+          <t>Osborn</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>natalie@cglfinancial.com</t>
+          <t>docoz@rogers.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1611,17 +1695,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Karli</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cabral</t>
+          <t>Roberts</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>emmadawn@bell.net</t>
+          <t>karlimaureen94@gmail.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1633,17 +1717,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ross</t>
+          <t>Saad</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Daqar</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ross@ideas2profit.ca</t>
+          <t>saad_dq@yahoo.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1655,17 +1739,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>George</t>
+          <t>Danielle</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cabral</t>
+          <t>VanderSteen</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>g_dog@bell.net</t>
+          <t>danielle.vandersteen2@gmail.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1677,17 +1761,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Naga</t>
+          <t>Maurice</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mullapudi</t>
+          <t>Lesperance</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>nagasaijyothim@gmail.com</t>
+          <t>maurice@primaklean.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1699,15 +1783,19 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sreesarani</t>
+          <t>Pickleplex</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mullapudi</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>Brantford</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1717,15 +1805,19 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Ayaan</t>
+          <t>Colleen</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Bhargava</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>Quinlan</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>momofchloeq@aol.com</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1735,15 +1827,19 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Vivaan</t>
+          <t>Vicki</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Bhargava</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>Ringelberg</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>vringelberg@gmail.com</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1753,17 +1849,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Beth</t>
+          <t>Madonna</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>McAllister</t>
+          <t>Adrian</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>beth.mcallister@bchsys.org</t>
+          <t>adrianmadonna3@gmail.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1775,17 +1871,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Wendy</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Chan</t>
+          <t>Hamilton</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>gregc@pickleplex.ca</t>
+          <t>whami4u2@outlook.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1797,15 +1893,19 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Lennox</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Fallis</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>Aird</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>jschafrick@hotmail.com</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1815,15 +1915,19 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Derek</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>deVries</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>Mazzetti</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>susanmazzetti@gmail.com</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1833,12 +1937,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Anna Laine</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Gosse</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1851,12 +1955,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Rikayla</t>
+          <t>Yeshe</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Baldin</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1869,15 +1973,19 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Kait</t>
+          <t>Sandi</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ayers</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>Capton</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>sandicapton_19@outlook.com</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1887,12 +1995,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Tanner</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Baldin</t>
+          <t>Lewis</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1905,15 +2013,19 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Jerika</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>deVries</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>Zandstra</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>jeremyzboy@gmail.com</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1923,15 +2035,19 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t>Ralph</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Bonnie</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
+          <t>Miller</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ralphmiller717@gmail.com</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1941,12 +2057,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Alexia</t>
+          <t>Jadea</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Zographos</t>
+          <t>Collin</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1959,12 +2075,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Shawn</t>
+          <t>Tyrese</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Corey</t>
+          <t>Collin</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1977,15 +2093,19 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Natasha</t>
+          <t>Sunny</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Muriithi</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>Mattu</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>matsunny@gmail.com</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -1995,15 +2115,19 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Allan</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Muriithi</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
+          <t>Sonola</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>tolulopejohnsyn@gmail.com</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2013,12 +2137,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>Enzo</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Njeru</t>
+          <t>Fernandaz</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -2031,12 +2155,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Jim</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ndungu</t>
+          <t>Miles</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -2049,12 +2173,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Hannah</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t>Miles</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -2067,19 +2191,15 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cristine</t>
+          <t>Emily</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Misiak</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>cristinemisiak@gmail.com</t>
-        </is>
-      </c>
+          <t>Drake</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2089,15 +2209,19 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Payton</t>
+          <t>Keisha</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Fennema</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
+          <t>Francis</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>keishaforsythe@hotmail.com</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2107,17 +2231,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Elysia</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Disher-Neddow</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>daireedelite@gmail.com</t>
+          <t>blackelysia@gmail.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2129,15 +2253,19 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Tarah</t>
+          <t>Carmen</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Pennings</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
+          <t>Arico</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>arico.cm@gmail.com</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2147,12 +2275,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Anika</t>
+          <t>Savitra</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Walsh</t>
+          <t>Sapre</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -2165,12 +2293,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Kelsey</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Pennings</t>
+          <t>Russell</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -2183,12 +2311,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Ellien</t>
+          <t>Eliana</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Pennings</t>
+          <t>Dionisio</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -2201,15 +2329,19 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Pennings</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
+          <t>Rodriguez</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>maria@yahoo.ca</t>
+        </is>
+      </c>
       <c r="D90" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2219,19 +2351,15 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>alexandria</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>lex_street@hotmail.com</t>
-        </is>
-      </c>
+          <t>Brouwer</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2241,15 +2369,19 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Rajan</t>
+          <t>William</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Jain Chouhan</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
+          <t>Clark</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>wclark@northwestrubber.com</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2259,19 +2391,15 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Arunkumar</t>
+          <t>Birkley</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>sujamol</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>arunjayakumarqlnv@gmail.com</t>
-        </is>
-      </c>
+          <t>Swan (Birka)</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2281,17 +2409,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Darwan</t>
+          <t>Carla</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Wilsin</t>
+          <t>Arsenault</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>darrenwilsin46@gmail.com</t>
+          <t>carlaarsenault14@gmail.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2303,17 +2431,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Arun</t>
+          <t>Nadine</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>kv</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>arunvnu444@gmail.com</t>
+          <t>nadine@springss.ca</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2325,19 +2453,15 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sunson</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Thomas</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>sunsonthomas10@gmail.com</t>
-        </is>
-      </c>
+          <t>Bylsma</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2347,15 +2471,19 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Wyatt</t>
+          <t>Tom</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Cook</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
+          <t>Hodgson</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>henleybobbie@gmail.com</t>
+        </is>
+      </c>
       <c r="D97" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2365,17 +2493,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Demaya</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Jenkins</t>
+          <t>Keen</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>toptiertipss@gmail.com</t>
+          <t>jennkeen@live.com</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2387,19 +2515,15 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Marty</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ditchburn</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>marty.ditchburn@gmail.com</t>
-        </is>
-      </c>
+          <t>Vornbrock</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2409,19 +2533,15 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Anu</t>
+          <t>Hrudik</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ajith</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>ananthuajith03@gmail.com</t>
-        </is>
-      </c>
+          <t>Mullapudi</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2431,19 +2551,15 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Eleanor</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Vandenbrink</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>ellie.vancasey@protonmail.com</t>
-        </is>
-      </c>
+          <t>Vornbrock</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2453,17 +2569,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Joel</t>
+          <t>Jerlaine</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>McKinnon</t>
+          <t>Oracion</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>joeljmckinnon@gmail.com</t>
+          <t>jerlaine_19@hotmail.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2475,17 +2591,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Amy</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MacMillan</t>
+          <t>Menegaldo</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>amy26mac@icloud.com</t>
+          <t>slapshot1192@gmail.com</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2497,17 +2613,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>annalise</t>
+          <t>Vicki</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>gadsby</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>annalisegadsby@gmail.com</t>
+          <t>v.edward@rogers.com</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2519,17 +2635,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Derek</t>
+          <t>Liz</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Lemaitre</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>derek.wbravo@gmail.com</t>
+          <t>lizlemaitre@gmail.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2541,19 +2657,15 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sophie</t>
+          <t>Abby</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Vandenbrink</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>sophie.vancasey@gmail.com</t>
-        </is>
-      </c>
+          <t>Caskie</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2563,17 +2675,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>McManamy</t>
+          <t>Mainse</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>mark.mcmanamy@gmail.com</t>
+          <t>ronmainse@gmail.com</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2585,19 +2697,15 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Gerald</t>
+          <t>Celine</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Shea</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>geraldshea1978@gmail.com</t>
-        </is>
-      </c>
+          <t>Prygiel</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2607,19 +2715,15 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Jen</t>
+          <t>Bianca</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Bravo</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>jenbravo19@gmail.com</t>
-        </is>
-      </c>
+          <t>Prygiel</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2629,17 +2733,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Ryleigh</t>
+          <t>Sang</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Lofgren</t>
+          <t>Tran</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ryleighstar@icloud.com</t>
+          <t>tiffanyhelenecarver@gmail.com</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2651,17 +2755,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BETH</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EKRON</t>
+          <t>Dunseith</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>beth.ekron@hotmail.com</t>
+          <t>jdunseith17@gmail.com</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2673,17 +2777,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Melanie</t>
+          <t>Norm</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Hastie</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>red.raven07@yahoo.com</t>
+          <t>norm.hasty@gmail.com</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2695,17 +2799,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Priya</t>
+          <t>Natalie</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Gita</t>
+          <t>Bodor</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>sivapriyag541@gmail.com</t>
+          <t>natalie@cglfinancial.com</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -2717,17 +2821,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Jaykumar</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Cabral</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>pateljayd97@gmail.com</t>
+          <t>emmadawn@bell.net</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -2739,17 +2843,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>Ross</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Rattle</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>jessrattle@hotmail.com</t>
+          <t>ross@ideas2profit.ca</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -2761,17 +2865,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>George</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Poos</t>
+          <t>Cabral</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>jesspoos@gmail.com</t>
+          <t>g_dog@bell.net</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -2783,17 +2887,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Kristen</t>
+          <t>Naga</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Lewis</t>
+          <t>Mullapudi</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>kristencar@hotmail.com</t>
+          <t>nagasaijyothim@gmail.com</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -2805,19 +2909,15 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Sreesarani</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Poos</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>kevindpoos@gmail.com</t>
-        </is>
-      </c>
+          <t>Mullapudi</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2827,19 +2927,15 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Katrina</t>
+          <t>Ayaan</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Dalton</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>katrinadalton3@gmail.com</t>
-        </is>
-      </c>
+          <t>Bhargava</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2849,19 +2945,15 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Jeanette</t>
+          <t>Vivaan</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Carnegie</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>jcarnegie5@hotmail.com</t>
-        </is>
-      </c>
+          <t>Bhargava</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2871,15 +2963,19 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>Will</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>shannelly</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr"/>
+          <t>Prygiel</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>will.prygiel@gmail.com</t>
+        </is>
+      </c>
       <c r="D121" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2889,17 +2985,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ISABELLA</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PAIXAO</t>
+          <t>Matthews</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>bellapaixao80@gmail.com</t>
+          <t>chris.matthews@whiteoaksgroup.ca</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -2911,17 +3007,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Beth</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Poos</t>
+          <t>McAllister</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>jpoos297@gmail.com</t>
+          <t>beth.mcallister@bchsys.org</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -2933,19 +3029,15 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Mary ann</t>
+          <t>Lennox</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Laughlin</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>mshannc614@rogers.com</t>
-        </is>
-      </c>
+          <t>Fallis</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2955,19 +3047,15 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Derek</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Belanger</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>bell.audrey@hotmail.com</t>
-        </is>
-      </c>
+          <t>deVries</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2977,19 +3065,15 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Farzaana</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Coovadia</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>farzaana.coovadia@gmail.com</t>
-        </is>
-      </c>
+          <t>Gosse</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -2999,19 +3083,15 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Rikayla</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Evans</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>uturntimmy@gmail.com</t>
-        </is>
-      </c>
+          <t>Baldin</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -3021,19 +3101,15 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Angel</t>
+          <t>Kait</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Evans</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>tjagevans@gmail.com</t>
-        </is>
-      </c>
+          <t>Ayers</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -3043,19 +3119,15 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Sharon</t>
+          <t>Tanner</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Rideout</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>skrideout@yahoo.ca</t>
-        </is>
-      </c>
+          <t>Baldin</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -3065,19 +3137,15 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Cole</t>
+          <t>Jerika</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Armitaje</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>cole_armatje@hotmail.com</t>
-        </is>
-      </c>
+          <t>deVries</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -3087,19 +3155,15 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Evan</t>
+          <t>Patrick</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Engell</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>evan@northshore.tax</t>
-        </is>
-      </c>
+          <t>Bonnie</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -3109,19 +3173,15 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>antoinette</t>
+          <t>Alexia</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>providence</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>aprovidedh8@gmail.com</t>
-        </is>
-      </c>
+          <t>Zographos</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -3131,19 +3191,15 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Fernando</t>
+          <t>Shawn</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Zefferino</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>fzeffer@gmail.com</t>
-        </is>
-      </c>
+          <t>Corey</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -3153,19 +3209,15 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Lynn</t>
+          <t>Natasha</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Joshi</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>lynn54099@gmail.com</t>
-        </is>
-      </c>
+          <t>Muriithi</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -3175,19 +3227,15 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Will</t>
+          <t>Allan</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Jansen</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>wjansen1919@gmail.com</t>
-        </is>
-      </c>
+          <t>Muriithi</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -3197,19 +3245,15 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Tom</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Engell</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>tomengell@outlook.com</t>
-        </is>
-      </c>
+          <t>Njeru</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -3219,19 +3263,15 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Laurie</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Zefferino</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>l.zefferino@gmail.com</t>
-        </is>
-      </c>
+          <t>Ndungu</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -3241,19 +3281,15 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Morton</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>mattmorton91@hotmail.com</t>
-        </is>
-      </c>
+          <t>Love</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -3263,17 +3299,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Izzy</t>
+          <t>Cristine</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Fortier</t>
+          <t>Misiak</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>fortierizzy@icloud.com</t>
+          <t>cristinemisiak@gmail.com</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -3285,17 +3321,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Kristen</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Rideout</t>
+          <t>Henderson</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>emma.rideout@hotmail.com</t>
+          <t>kristen@20paa.com</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3307,19 +3343,15 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Davis</t>
+          <t>Payton</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Wylie</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>dwylie793@gmail.com</t>
-        </is>
-      </c>
+          <t>Fennema</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -3329,17 +3361,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Jim</t>
+          <t>Krista</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Peitro</t>
+          <t>Hearn</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>gym.peitro@hotmail.com</t>
+          <t>krista.hearn@mcdonalds-luma.ca</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3351,17 +3383,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Amanda</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Roorda</t>
+          <t>Disher-Neddow</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>amanda.roorda@gmail.com</t>
+          <t>daireedelite@gmail.com</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -3373,19 +3405,15 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Tarah</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Olmstead</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>ljolms@hotmail.com</t>
-        </is>
-      </c>
+          <t>Pennings</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -3395,12 +3423,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Knox</t>
+          <t>Anika</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Morton</t>
+          <t>Walsh</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -3413,19 +3441,15 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Kelsey</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Horney</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>hazelnjh7@gmail.com</t>
-        </is>
-      </c>
+          <t>Pennings</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -3435,19 +3459,15 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Ellien</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Johnson</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>adamr.sr.84@gmail.com</t>
-        </is>
-      </c>
+          <t>Pennings</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -3457,19 +3477,15 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Cheri</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Ruprai</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>cbeaton99@yahoo.com</t>
-        </is>
-      </c>
+          <t>Pennings</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -3479,17 +3495,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Dustin</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Anderson</t>
+          <t>Leppard</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>thegang110@gmail.com</t>
+          <t>19lepp@gmail.com</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -3501,17 +3517,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Tammy</t>
+          <t>alexandria</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Davis</t>
+          <t>street</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>tjddavis71@gmail.com</t>
+          <t>lex_street@hotmail.com</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -3523,12 +3539,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Kendall</t>
+          <t>Rajan</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Morton</t>
+          <t>Jain Chouhan</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -3541,15 +3557,19 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>Valentina</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Morton</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr"/>
+          <t>Bernardi</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>vmbernardi@gmail.com</t>
+        </is>
+      </c>
       <c r="D152" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -3559,17 +3579,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Gord</t>
+          <t>Arunkumar</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Bryenton</t>
+          <t>sujamol</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>rosebryenton@hotmail.com</t>
+          <t>arunjayakumarqlnv@gmail.com</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -3581,17 +3601,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Natalie</t>
+          <t>Darwan</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Hein</t>
+          <t>Wilsin</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>nataliehein05@gmail.com</t>
+          <t>darrenwilsin46@gmail.com</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -3603,17 +3623,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Campbell</t>
+          <t>Arun</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>MacKinnon</t>
+          <t>kv</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>campbelljamesmackinnon@gmail.com</t>
+          <t>arunvnu444@gmail.com</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -3625,17 +3645,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Tori</t>
+          <t>Sunson</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Sitwell</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>tori_stiwell@hotmail.com</t>
+          <t>sunsonthomas10@gmail.com</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -3647,19 +3667,15 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Brandy</t>
+          <t>Wyatt</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Spence</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>gbspence@rogers.com</t>
-        </is>
-      </c>
+          <t>Cook</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -3669,17 +3685,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Demaya</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Spence</t>
+          <t>Jenkins</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>gbspence@gmail.com</t>
+          <t>toptiertipss@gmail.com</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -3691,17 +3707,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Todd</t>
+          <t>Marty</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>McPherson</t>
+          <t>Ditchburn</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>todd_mcp@yahoo.com</t>
+          <t>marty.ditchburn@gmail.com</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -3713,17 +3729,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Isabel</t>
+          <t>Anu</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Simmons</t>
+          <t>Ajith</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>isabel.simmons@icloud.com</t>
+          <t>ananthuajith03@gmail.com</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -3735,17 +3751,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Jake</t>
+          <t>Eleanor</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Vandenbrink</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>jacobw.paul@outlook.com</t>
+          <t>ellie.vancasey@protonmail.com</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -3757,17 +3773,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>karina</t>
+          <t>Joel</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>morrison</t>
+          <t>McKinnon</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>karinaditchburn21@gmail.com</t>
+          <t>joeljmckinnon@gmail.com</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -3779,17 +3795,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>alicia</t>
+          <t>Amy</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ditchburn</t>
+          <t>MacMillan</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>aliciaditchburn51@gmail.com</t>
+          <t>amy26mac@icloud.com</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -3801,17 +3817,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>annalise</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Slattery</t>
+          <t>gadsby</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>david.slattery@outlook.com</t>
+          <t>annalisegadsby@gmail.com</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -3823,17 +3839,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Connor</t>
+          <t>Derek</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Crickmore</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>connor.crickmore@icloud.com</t>
+          <t>derek.wbravo@gmail.com</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -3845,17 +3861,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>amy</t>
+          <t>Sophie</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ditchburn</t>
+          <t>Vandenbrink</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>amy.ditchburn54@gmail.com</t>
+          <t>sophie.vancasey@gmail.com</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -3867,17 +3883,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Ashton</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Welsh</t>
+          <t>McManamy</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>ashtoncwelsh@gmail.com</t>
+          <t>mark.mcmanamy@gmail.com</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -3889,17 +3905,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Cam</t>
+          <t>Gerald</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Welsh</t>
+          <t>Shea</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>cameronmwelsh@gmail.com</t>
+          <t>geraldshea1978@gmail.com</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -3911,17 +3927,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>wesley</t>
+          <t>Jen</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>bramham</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>cameronmatthewwelsh@gmail.com</t>
+          <t>jenbravo19@gmail.com</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -3933,17 +3949,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Hadeer</t>
+          <t>Ryleigh</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Dawood</t>
+          <t>Lofgren</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>hadeerdawoodd@icloud.com</t>
+          <t>ryleighstar@icloud.com</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -3955,17 +3971,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Arunkumar</t>
+          <t>BETH</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Jayakumar Sujamol</t>
+          <t>EKRON</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>arunjayakumarqlnd@gmail.com</t>
+          <t>beth.ekron@hotmail.com</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -3977,15 +3993,19 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Melanie</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Lowther</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr"/>
+          <t>Cabrera</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>red.raven07@yahoo.com</t>
+        </is>
+      </c>
       <c r="D172" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -3995,17 +4015,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Joyce</t>
+          <t>Priya</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Sage</t>
+          <t>Gita</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>joyce_sage@hotmail.com</t>
+          <t>sivapriyag541@gmail.com</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -4017,17 +4037,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Émilie-Céline</t>
+          <t>Jaykumar</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Lowther</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>drgnflysmith@gmail.com</t>
+          <t>pateljayd97@gmail.com</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -4039,15 +4059,19 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Areej</t>
+          <t>Jessica</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Naseer</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr"/>
+          <t>Rattle</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>jessrattle@hotmail.com</t>
+        </is>
+      </c>
       <c r="D175" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -4057,17 +4081,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Trevor</t>
+          <t>Jessica</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Poos</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>sales.bowmanville@hotmail.com</t>
+          <t>jesspoos@gmail.com</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -4079,17 +4103,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Simon</t>
+          <t>Kristen</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Gonzalez</t>
+          <t>Lewis</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>simon.gonzalez.n@icloud.com</t>
+          <t>kristencar@hotmail.com</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -4101,17 +4125,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Wania</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Ashfaq</t>
+          <t>Poos</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>sadafsaki786@gmail.com</t>
+          <t>kevindpoos@gmail.com</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -4123,17 +4147,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Sheryl</t>
+          <t>Katrina</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Van Kruistum</t>
+          <t>Dalton</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>savk1096@gmail.com</t>
+          <t>katrinadalton3@gmail.com</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -4145,19 +4169,15 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Pablo</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Gonzalez</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>pablogonar2004@icloud.com</t>
-        </is>
-      </c>
+          <t>shannelly</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -4167,17 +4187,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Fatema</t>
+          <t>ISABELLA</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Alashmouti</t>
+          <t>PAIXAO</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>fatima_ashmouti@icloud.com</t>
+          <t>bellapaixao80@gmail.com</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -4189,17 +4209,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Garett</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Korber</t>
+          <t>Poos</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>sgkorber@sympatico.ca</t>
+          <t>jpoos297@gmail.com</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -4211,17 +4231,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Emaan</t>
+          <t>Mary ann</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Daud</t>
+          <t>Laughlin</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>emaandaud504@icloud.com</t>
+          <t>mshannc614@rogers.com</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -4233,15 +4253,19 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Fatima</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Safdar</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr"/>
+          <t>Belanger</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>bell.audrey@hotmail.com</t>
+        </is>
+      </c>
       <c r="D184" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -4251,17 +4275,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Nikki</t>
+          <t>Farzaana</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Nuun</t>
+          <t>Coovadia</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>nikkinuun@msn.com</t>
+          <t>farzaana.coovadia@gmail.com</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -4273,15 +4297,19 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Dua</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Safdar</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr"/>
+          <t>Evans</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>uturntimmy@gmail.com</t>
+        </is>
+      </c>
       <c r="D186" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -4291,17 +4319,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Lateefah</t>
+          <t>Angel</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Binuyo</t>
+          <t>Evans</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>lateefahbinuyo@gmail.com</t>
+          <t>tjagevans@gmail.com</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -4313,17 +4341,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Julieta</t>
+          <t>Sharon</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Narvaez</t>
+          <t>Rideout</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>narvaezjulieta@yahoo.com</t>
+          <t>skrideout@yahoo.ca</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -4335,17 +4363,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Zainab</t>
+          <t>Crosby</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Naseer</t>
+          <t>Gibson</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>naseerzainab85@gmail.com</t>
+          <t>crosby.gibson@rogers.com</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -4357,17 +4385,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Farzana</t>
+          <t>Cole</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Kausar</t>
+          <t>Armitaje</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>farzanakausar25@gmail.com</t>
+          <t>cole_armatje@hotmail.com</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -4379,15 +4407,19 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Caisha</t>
+          <t>Evan</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Nuun</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr"/>
+          <t>Engell</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>evan@northshore.tax</t>
+        </is>
+      </c>
       <c r="D191" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -4397,17 +4429,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Durrah</t>
+          <t>antoinette</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Adil</t>
+          <t>providence</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>durrah869@gmail.com</t>
+          <t>aprovidedh8@gmail.com</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -4419,17 +4451,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Karida</t>
+          <t>Fernando</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Ansary</t>
+          <t>Zefferino</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>taj.nesa@yahoo.ca</t>
+          <t>fzeffer@gmail.com</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -4441,17 +4473,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Lynn</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Van Kruistum</t>
+          <t>Joshi</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>tavk1081@gmail.com</t>
+          <t>lynn54099@gmail.com</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -4463,15 +4495,19 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Hodan</t>
+          <t>Will</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Nuun</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr"/>
+          <t>Jansen</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>wjansen1919@gmail.com</t>
+        </is>
+      </c>
       <c r="D195" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -4481,17 +4517,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>rachel</t>
+          <t>Tom</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>bryant</t>
+          <t>Engell</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>rachelbryant838@gmail.com</t>
+          <t>tomengell@outlook.com</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -4503,17 +4539,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Elaine</t>
+          <t>Laurie</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Hazlett</t>
+          <t>Zefferino</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>thehazletts@rogers.com</t>
+          <t>l.zefferino@gmail.com</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -4525,17 +4561,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>arwa</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>rostom</t>
+          <t>Morton</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>arwarostom13@gmail.com</t>
+          <t>mattmorton91@hotmail.com</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -4547,17 +4583,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>zeliha</t>
+          <t>Izzy</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>demir</t>
+          <t>Fortier</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>zelihad696@gmail.com</t>
+          <t>fortierizzy@icloud.com</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -4569,17 +4605,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Lamar</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Dawood</t>
+          <t>Rideout</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>ruqaya.ahmed22@gmail.com</t>
+          <t>emma.rideout@hotmail.com</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -4591,17 +4627,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Ghazal</t>
+          <t>Davis</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Alashmouti</t>
+          <t>Wylie</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>galashmouti@icloud.com</t>
+          <t>dwylie793@gmail.com</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -4613,17 +4649,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Aiza</t>
+          <t>Jim</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Tayyeb</t>
+          <t>Peitro</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>aiza14tayyeb@gmail.com</t>
+          <t>gym.peitro@hotmail.com</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -4635,17 +4671,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Nilda</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Merza</t>
+          <t>Hernandez</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>s.mrza.1504@gmail.com</t>
+          <t>np_h100@yahoo.com</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -4657,17 +4693,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Andres</t>
+          <t>Amanda</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Gonzalez</t>
+          <t>Roorda</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>afgon@hotmail.com</t>
+          <t>amanda.roorda@gmail.com</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -4679,17 +4715,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Zaynah</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Molani</t>
+          <t>Olmstead</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>zaynahmolani@gmail.com</t>
+          <t>ljolms@hotmail.com</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -4701,19 +4737,15 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Robina</t>
+          <t>Knox</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Rafique</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>robina.rafique@gmail.com</t>
-        </is>
-      </c>
+          <t>Morton</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -4723,15 +4755,19 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Manal</t>
+          <t>Jane</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Naseer</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr"/>
+          <t>Horney</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>hazelnjh7@gmail.com</t>
+        </is>
+      </c>
       <c r="D207" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -4741,15 +4777,19 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Kendall</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Morton</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr"/>
+          <t>Johnson</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>adamr.sr.84@gmail.com</t>
+        </is>
+      </c>
       <c r="D208" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -4759,17 +4799,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Salicia</t>
+          <t>Cheri</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Postam</t>
+          <t>Ruprai</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>saliciap48@gmail.com</t>
+          <t>cbeaton99@yahoo.com</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -4781,17 +4821,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Donna</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Hood</t>
+          <t>Anderson</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>hoodd@rogers.com</t>
+          <t>thegang110@gmail.com</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -4803,17 +4843,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Tammy</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Davis</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>klm.austin@cogeco.ca</t>
+          <t>tjddavis71@gmail.com</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -4825,7 +4865,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>Kendall</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -4833,11 +4873,7 @@
           <t>Morton</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>jessicahead@hotmail.com</t>
-        </is>
-      </c>
+      <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
@@ -4847,7 +4883,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Knox</t>
+          <t>Jessica</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -4857,6 +4893,3296 @@
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Darryl</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Van Sickle</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>vansickledarryl@gmail.com</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Nicklaus</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Csuzdi</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>nicklauscsuzdi@gmail.com</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Gord</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Bryenton</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>rosebryenton@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Natalie</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Hein</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>nataliehein05@gmail.com</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Campbell</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>MacKinnon</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>campbelljamesmackinnon@gmail.com</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Tori</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Sitwell</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>tori_stiwell@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Brandy</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Spence</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>gbspence@rogers.com</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Greg</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Spence</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>gbspence@gmail.com</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Todd</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>McPherson</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>todd_mcp@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Isabel</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Simmons</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>isabel.simmons@icloud.com</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Jake</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>jacobw.paul@outlook.com</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>karina</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>morrison</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>karinaditchburn21@gmail.com</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>alicia</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>ditchburn</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>aliciaditchburn51@gmail.com</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Slattery</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>david.slattery@outlook.com</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Connor</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Crickmore</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>connor.crickmore@icloud.com</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>amy</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>ditchburn</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>amy.ditchburn54@gmail.com</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Ashton</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Welsh</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>ashtoncwelsh@gmail.com</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Cam</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Welsh</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>cameronmwelsh@gmail.com</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>wesley</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>bramham</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>cameronmatthewwelsh@gmail.com</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Hadeer</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Dawood</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>hadeerdawoodd@icloud.com</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Ishan</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Sharma</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>ishan.92005@gmail.com</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Arunkumar</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Jayakumar Sujamol</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>arunjayakumarqlnd@gmail.com</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Lowther</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Joyce</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Sage</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>joyce_sage@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Émilie-Céline</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Lowther</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>drgnflysmith@gmail.com</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Areej</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Naseer</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Trevor</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>sales.bowmanville@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Simon</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Gonzalez</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>simon.gonzalez.n@icloud.com</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Wania</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Ashfaq</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>sadafsaki786@gmail.com</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Sheryl</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Van Kruistum</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>savk1096@gmail.com</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Gonzalez</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>pablogonar2004@icloud.com</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Fatema</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Alashmouti</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>fatima_ashmouti@icloud.com</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Garett</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Korber</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>sgkorber@sympatico.ca</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Emaan</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Daud</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>emaandaud504@icloud.com</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Fatima</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Safdar</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Nikki</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Nuun</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>nikkinuun@msn.com</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Dua</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Safdar</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Lateefah</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Binuyo</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>lateefahbinuyo@gmail.com</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Julieta</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Narvaez</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>narvaezjulieta@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Zainab</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Naseer</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>naseerzainab85@gmail.com</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Farzana</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Kausar</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>farzanakausar25@gmail.com</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Caisha</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Nuun</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Durrah</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Adil</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>durrah869@gmail.com</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Karida</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Ansary</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>taj.nesa@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Van Kruistum</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>tavk1081@gmail.com</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Hodan</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Nuun</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>rachel</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>bryant</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>rachelbryant838@gmail.com</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Elaine</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Hazlett</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>thehazletts@rogers.com</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>arwa</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>rostom</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>arwarostom13@gmail.com</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>zeliha</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>demir</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>zelihad696@gmail.com</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Lamar</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Dawood</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>ruqaya.ahmed22@gmail.com</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Ghazal</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Alashmouti</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>galashmouti@icloud.com</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Aiza</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Tayyeb</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>aiza14tayyeb@gmail.com</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Merza</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>s.mrza.1504@gmail.com</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Andres</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Gonzalez</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>afgon@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Zaynah</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Molani</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>zaynahmolani@gmail.com</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Robina</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Rafique</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>robina.rafique@gmail.com</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Manal</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Naseer</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Kendall</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Morton</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Salicia</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Postam</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>saliciap48@gmail.com</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Donna</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Hood</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>hoodd@rogers.com</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>klm.austin@cogeco.ca</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Jessica</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Morton</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>jessicahead@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Knox</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Morton</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Tavinder</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Gill</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>tavinder.gill@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Gurinder</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Sandhu</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>gurindersandhu@live.ca</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Gill</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>gillpeter170@outlook.com</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Pavandeep</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Gill</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>pavangill6@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>JV</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Sharlene</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Todd</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>shar42@live.com</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Rajwinder</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>gill</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>raji2615@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Jaden</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Hill</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>jadenhill_10@icloud.com</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Octacilio</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>octaciliojr@gmail.com</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Jasdeep</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>gill</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>jasdeepgill4@outlook.com</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Romeo</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Buenaventura</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>rbuenaventu0612@gmail.com</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Annu</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Gill</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>gillannuk@gmail.com</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Elizabeth</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Capitano</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>capitano2804@gmail.com</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Aiden</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Beaudoin</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>aidenbeaudoin@gmail.com</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Jen</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Coombe</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>jen_logan@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Chris</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>frenchy-12@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Tudo</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>atudo1@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Breyden</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Miller</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>healthyliving@briscfc.org</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Miller</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>char.miller@live.com</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Sara</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Barrieau</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>sarabarrieau@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Whitney</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>jaimeleewhitney@gmail.com</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Julianne</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Powell</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>jtovstiga@gmail.com</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Powell</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>wolftp49@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Powell</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>mpowell3833@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Kadian</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Datadeen</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>kaynem16@icloud.com</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Linda</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Uderika</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>somaegbuna@gmail.com</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Anh</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Nguyen</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>anhnguyen647@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Riya</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Mehta</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>riyamehta1210@gmail.com</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Parvinder</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Sahota</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>parvindersahota20@gmail.com</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Carlee</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Webb</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>carleebond27@gmail.com</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Debi</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Rennie</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>scotia@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Ty</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Humpartzoomian</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>tyhumpaetzoomian@gmail.com</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Manav</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Patel</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Hardik</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Patel</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>hardik3969@gmail.com</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Varun</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Sutti</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>varunsutti@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Rihaan</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Ray</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Neel</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Patel</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>nbpatel4092@gmail.com</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Drashti</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Patel</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>patteldrashti1575@gmail.com</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Nidha</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Ray</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>rayn8194@gmail.com</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Poonam</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>patel</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>patelpoonan182@gmail.com</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Tereza</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Mattatall</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>terezamattatall@gmail.com</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Arathi</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>aamjaaru007@gmail.com</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Abhishek</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Anilkumar</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>appu1998cfc@gmail.com</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Lauren</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Calbeck</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>laurencalbeck26@gmail.com</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Maeve</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Treleaven</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>maeve.treleaven@gmail.com</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>BettyAnn</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>bannmartin@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Ravinder</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Bhalla</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>ravibhalla@gmail.com</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>jennifer</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>kirkbride</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>jkirkbride@bell.net</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Lorna</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>McIntyre</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>lorna4346@aol.com</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Tina</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>tharris34@cogeco.ca</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Heather</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Vaughan</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>heather1.vaughan@gmail.com</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Manu</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Murali</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>manumurali20@gmail.com</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Suman</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Davanapalli</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>sumanosteo@gmail.com</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Shweta</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Mehta</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>arora.shweta21@gmail.com</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Megan</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Hammill</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>meganhammill@outlook.com</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Robin</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Whitbread</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>robin.whitbread@sympatico.ca</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Thao</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>thaotjoseph@gmail.com</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Gladys</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Rodgers</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>gladysrodgers@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Minnie</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>McBlain</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>minniemcblain@gmail.com</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Bradley</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>monica0207@gmail.com</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Ty</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Humpartzoomian</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>tyhumpartzoomian@gmail.com</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Philip</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Kelly</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>pklovestoski@gmail.com</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Mitro</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>paul.mitro@gmail.com</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Amanda</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Naveas</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Izzy</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Fallis</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Viola</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>viola.gabriel@rogers.com</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Mccracken</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>trish_mcc@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Carolina</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Naveas</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>caro.olivares@gmail.com</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>darion</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>boyington</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>boyingtondarion@gmail.com</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Matilda</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Naveas</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Amrit</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Sahota</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>amritsahota1996@gmail.com</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Ema</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Naveas</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Blake</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Hughes</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Ines</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Puyol</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>inespuyol639@gmail.com</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Niall</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Richardson</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>niallrichardson97@gmail.com</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Christine</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Morris-Bolton</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>cmorrisbolton@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Bolton</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>mbolton009@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Adaline</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Raflac</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Axel</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Raflac</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Jerome</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Richardson</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>jmr6008@gmail.com</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Naveas</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>pnavaes@gmail.com</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Brandon</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Hume</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>bnhume@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Lynn</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Skirrow</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>lynn.skirrow@gmail.com</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Karen</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Blaak</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>karen.blaak@rogers.com</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Lisa</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Lauzon</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>lisa.lauzon2@icloud.com</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Claudia</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Vodola</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>claudiavodola@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Wendy</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Hamilton</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>whamilton89@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Patti</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Meggitt</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>kirkpatti2304@gmail.com</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>brantford@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Luiz</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>luizfad@gmail.com</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
         <is>
           <t>brantford@pickleplex.ca</t>
         </is>
